--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.4.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.4.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1055,7 +1055,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.4.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.4.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y128"/>
+  <dimension ref="A1:Y138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00219_18600707\oocihm.N_00219_18600707.4.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00219_18600707\oocihm.N_00219_18600707.4.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.4.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.4.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -617,16 +617,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L7: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: For any one e the four Reviews.â€¦...</t>
+          <t>L64: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: Yearly, 85; Half-yearly. 2.50 ； Quarter-</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: Â¥-</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L18: isolated marker/symbol line :: 2</t>
@@ -634,17 +638,17 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
         <is>
-          <t>L7: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: For any one e the four Reviews.â€¦...</t>
+          <t>L7: punctuation artifact: repeated periods :: For any one e the four Reviews.…...</t>
         </is>
       </c>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: quote/punctuation debris :: unto the third and fourth generation ; indeed, â€”., 171.</t>
+          <t>L136: punctuation artifact: repeated periods :: For any one of the four Reviews ...</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr">
@@ -665,7 +669,7 @@
       </c>
       <c r="V2" s="1" t="inlineStr">
         <is>
-          <t>L366: abbreviation/spacing may be garbled :: OF TORONTOÏ…. C.W.</t>
+          <t>L366: abbreviation/spacing may be garbled :: OF TORONTOυ. C.W.</t>
         </is>
       </c>
       <c r="W2" s="1" t="inlineStr">
@@ -689,7 +693,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>924</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -720,12 +724,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L10: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | possible duplicated/overlap line with previous line (similarity 70%) :: For all four of the Reviews, .â€¦, .â€¦â€¦</t>
+          <t>L86: stray/suspicious non-ASCII glyph(s): U+53E3 CJK UNIFIED IDEOGRAPH-53E3 | isolated marker/symbol line :: 口</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œthe cosmetics and other toilet</t>
+          <t>L5: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: ¥-</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -737,7 +741,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: Â¥-</t>
+          <t>L5: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: ¥-</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
@@ -747,7 +751,7 @@
       </c>
       <c r="Q3" s="1" t="inlineStr">
         <is>
-          <t>L136: punctuation artifact: repeated periods :: For any one of the four Reviews ...</t>
+          <t>L142: punctuation artifact: double/multiple hyphen :: For Blackwood’s Magazine, -------</t>
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr">
@@ -797,7 +801,7 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>L10: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | possible duplicated/overlap line with previous line (similarity 70%) :: For all four of the Reviews, .â€¦, .â€¦â€¦</t>
+          <t>L10: possible duplicated/overlap line with previous line (similarity 70%) :: For all four of the Reviews, .…, .……</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr"/>
@@ -823,12 +827,12 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L67: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‹</t>
+          <t>L286: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: OUR MUSICAL FRIEND. Scrofula, or Kingâ€™s Evil,</t>
+          <t>L77: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | suspicious token(s): s5 (letter/digit mix) :: 9 00 Yearly, s5; Half yearly 89.50 • Quarter-</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -850,13 +854,13 @@
       </c>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L142: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: double/multiple hyphen :: For Blackwoodâ€™s Magazine, -------</t>
+          <t>L185: punctuation artifact: repeated periods :: LEONARD SCOTT &amp; Co.. $2.50 each constantly on hand</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>L191: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ____________â€” ------------- ----: ---107 Nassau St., New York.</t>
+          <t>L79: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •Subscribe to . Our Musical Friend," or</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr"/>
@@ -878,12 +882,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>253</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>124</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
@@ -914,12 +918,12 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L68: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: Subscribe to "Our Musical Friend,â€� or</t>
+          <t>L304: stray/suspicious non-ASCII glyph(s): U+4E0A CJK UNIFIED IDEOGRAPH-4E0A | isolated marker/symbol line :: 上</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L54: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”is a constitutional disease, a corruption of the</t>
+          <t>L79: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •Subscribe to . Our Musical Friend," or</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -941,19 +945,19 @@
       </c>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>L185: punctuation artifact: repeated periods :: LEONARD SCOTT &amp; Co.. $2.50 each constantly on hand</t>
+          <t>L191: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ____________— ------------- ----: ---107 Nassau St., New York.</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
       <c r="S5" s="1" t="inlineStr">
         <is>
-          <t>L234: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: --cessful practice in Europe and America</t>
+          <t>L191: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ____________— ------------- ----: ---107 Nassau St., New York.</t>
         </is>
       </c>
       <c r="T5" s="1" t="inlineStr"/>
       <c r="U5" s="1" t="inlineStr">
         <is>
-          <t>L940: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): thartiePill (odd internal casing) | missing space around punctuation :: thartiePill has,with Â© Rheumatism, a great | I London. Sold retail by all Druggists and Pa-</t>
+          <t>L940: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): thartiePill (odd internal casing) | missing space around punctuation :: thartiePill has,with © Rheumatism, a great | I London. Sold retail by all Druggists and Pa-</t>
         </is>
       </c>
       <c r="V5" s="1" t="inlineStr"/>
@@ -1000,17 +1004,17 @@
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): s5 (letter/digit mix) :: 9 00 Yearly, s5; Half yearly 89.50 â€¢ Quarter-</t>
+          <t>L77: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | suspicious token(s): s5 (letter/digit mix) :: 9 00 Yearly, s5; Half yearly 89.50 • Quarter-</t>
         </is>
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å�£</t>
+          <t>L350: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): s5 (letter/digit mix) :: 9 00 Yearly, s5; Half yearly 89.50 â€¢ Quarter-</t>
+          <t>L111: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: it seems to be the rod of Him who says, •• I Both the Ointment and Pills should be</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -1032,13 +1036,13 @@
       </c>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L191: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ____________â€” ------------- ----: ---107 Nassau St., New York.</t>
+          <t>L230: punctuation artifact: double/multiple hyphen :: _— ______________- ----------------— The treatment they adopt is the result of</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
       <c r="S6" s="1" t="inlineStr">
         <is>
-          <t>L292: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | line starts with punctuation glued to text :: _________________________â€” â€” correct detail of their cases witha remit-</t>
+          <t>L234: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: --cessful practice in Europe and America</t>
         </is>
       </c>
       <c r="T6" s="1" t="inlineStr"/>
@@ -1088,12 +1092,12 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L107: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: situation, descending â€œfrom parents to children</t>
+          <t>L374: stray/suspicious non-ASCII glyph(s): U+88C5 CJK UNIFIED IDEOGRAPH-88C5 | isolated marker/symbol line :: 装</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢Subscribe to . Our Musical Friend," or</t>
+          <t>L285: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •information to be had on applying at the complaints, or from whom genuine European , ALICE Tell</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -1115,13 +1119,13 @@
       </c>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>L230: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: _â€” ______________- ----------------â€” The treatment they adopt is the result of</t>
+          <t>L234: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: --cessful practice in Europe and America</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
       <c r="S7" s="1" t="inlineStr">
         <is>
-          <t>L311: line starts with punctuation glued to text :: .the experience of one nation, but consists of</t>
+          <t>L285: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •information to be had on applying at the complaints, or from whom genuine European , ALICE Tell</t>
         </is>
       </c>
       <c r="T7" s="1" t="inlineStr"/>
@@ -1167,12 +1171,12 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L304: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA :: ä¸Š</t>
+          <t>L381: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: quote/punctuation debris :: unto the third and fourth generation ; indeed, â€”., 171.</t>
+          <t>L289: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen :: 1. C HART, Persons IN ANY PART OF THE WORLD • of -----</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
@@ -1184,7 +1188,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L390: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L390: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr">
@@ -1194,13 +1198,13 @@
       </c>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L234: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: --cessful practice in Europe and America</t>
+          <t>L246: punctuation artifact: repeated periods :: VALLA..............DR. AMOS &amp; SON takes pleasure in rilla is to purify and regenerate thisvitalfluid,</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
       <c r="S8" s="1" t="inlineStr">
         <is>
-          <t>L474: line starts with punctuation glued to text :: ** Sold at the Manufactory of Professor</t>
+          <t>L292: line starts with punctuation glued to text :: _________________________— — correct detail of their cases witha remit-</t>
         </is>
       </c>
       <c r="T8" s="1" t="inlineStr"/>
@@ -1246,12 +1250,12 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L381: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L467: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L111: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: it seems to be the rod of Him who says, â€¢â€¢ I Both the Ointment and Pills should be</t>
+          <t>L390: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
@@ -1268,18 +1272,18 @@
       </c>
       <c r="P9" s="1" t="inlineStr">
         <is>
-          <t>L392: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: Head Office... â€¦. Church Street. Toronto:</t>
+          <t>L392: punctuation artifact: repeated periods :: Head Office... …. Church Street. Toronto:</t>
         </is>
       </c>
       <c r="Q9" s="1" t="inlineStr">
         <is>
-          <t>L246: punctuation artifact: repeated periods :: VALLA..............DR. AMOS &amp; SON takes pleasure in rilla is to purify and regenerate thisvitalfluid,</t>
+          <t>L268: punctuation artifact: repeated periods :: Head Office....Church Street, Toronto: Persons wishing the above usefulinstru-</t>
         </is>
       </c>
       <c r="R9" s="1" t="inlineStr"/>
       <c r="S9" s="1" t="inlineStr">
         <is>
-          <t>L551: line starts with punctuation glued to text :: .ROBE</t>
+          <t>L311: line starts with punctuation glued to text :: .the experience of one nation, but consists of</t>
         </is>
       </c>
       <c r="T9" s="1" t="inlineStr"/>
@@ -1297,12 +1301,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1325,12 +1329,12 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L392: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: Head Office... â€¦. Church Street. Toronto:</t>
+          <t>L596: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L142: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: double/multiple hyphen :: For Blackwoodâ€™s Magazine, -------</t>
+          <t>L398: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • YS</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
@@ -1352,13 +1356,13 @@
       </c>
       <c r="Q10" s="1" t="inlineStr">
         <is>
-          <t>L268: punctuation artifact: repeated periods :: Head Office....Church Street, Toronto: Persons wishing the above usefulinstru-</t>
+          <t>L289: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen :: 1. C HART, Persons IN ANY PART OF THE WORLD • of -----</t>
         </is>
       </c>
       <c r="R10" s="1" t="inlineStr"/>
       <c r="S10" s="1" t="inlineStr">
         <is>
-          <t>L591: line starts with punctuation glued to text :: .Dysentery. Dropsy</t>
+          <t>L398: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • YS</t>
         </is>
       </c>
       <c r="T10" s="1" t="inlineStr"/>
@@ -1381,7 +1385,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1404,12 +1408,12 @@
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L457: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): m0s (letter/digit mix) :: m0sâ€ skeptical as to the merits of their in-</t>
+          <t>L723: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L191: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ____________â€” ------------- ----: ---107 Nassau St., New York.</t>
+          <t>L443: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: known in the world for the•</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
@@ -1427,13 +1431,13 @@
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>L289: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: 1. C HART, Persons IN ANY PART OF THE WORLD â€¢ of -----</t>
+          <t>L329: punctuation artifact: repeated periods :: From the time I first discovered its dropp ng..</t>
         </is>
       </c>
       <c r="R11" s="1" t="inlineStr"/>
       <c r="S11" s="1" t="inlineStr">
         <is>
-          <t>L599: line starts with digit/letter garbage token | suspicious token(s): 1Morbus (letter/digit mix) :: 1Morbus, I give it to you at the request of Mr Bradford</t>
+          <t>L474: line starts with punctuation glued to text :: ** Sold at the Manufactory of Professor</t>
         </is>
       </c>
       <c r="T11" s="1" t="inlineStr"/>
@@ -1451,7 +1455,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>137</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1479,19 +1483,19 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>L467: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L748: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L202: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: or cash, at Bruceâ€™s New York Type Foundry.</t>
+          <t>L506: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Hair Restorative’ which he liked very much</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L67: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‹</t>
+          <t>L67: isolated marker/symbol line :: 》</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
@@ -1502,13 +1506,13 @@
       <c r="P12" s="1" t="inlineStr"/>
       <c r="Q12" s="1" t="inlineStr">
         <is>
-          <t>L329: punctuation artifact: repeated periods :: From the time I first discovered its dropp ng..</t>
+          <t>L367: punctuation artifact: double/multiple hyphen :: Such a medicine we supply in - -----——</t>
         </is>
       </c>
       <c r="R12" s="1" t="inlineStr"/>
       <c r="S12" s="1" t="inlineStr">
         <is>
-          <t>L644: line starts with punctuation glued to text :: .tifiestesin my pos</t>
+          <t>L506: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Hair Restorative’ which he liked very much</t>
         </is>
       </c>
       <c r="T12" s="1" t="inlineStr"/>
@@ -1554,12 +1558,12 @@
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>L596: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L771: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L220: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: taining it. will be allowed his bill, at the time â€” New York,</t>
+          <t>L601: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: €holers Infantum You can sell a great deal of your Hair Resto-</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
@@ -1571,19 +1575,19 @@
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L791: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
+          <t>L791: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr">
         <is>
-          <t>L367: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: Such a medicine we supply in - -----â€”â€”</t>
+          <t>L517: punctuation artifact: repeated periods :: ing the larger sizes..</t>
         </is>
       </c>
       <c r="R13" s="1" t="inlineStr"/>
       <c r="S13" s="1" t="inlineStr">
         <is>
-          <t>L842: line starts with punctuation glued to text :: .w high all express in ly. if neglected, end which have now stood the test of public exp-</t>
+          <t>L551: line starts with punctuation glued to text :: .ROBE</t>
         </is>
       </c>
       <c r="T13" s="1" t="inlineStr"/>
@@ -1606,7 +1610,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1629,19 +1633,19 @@
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>L723: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L833: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>L226: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: GEORGE BRUCE. 8 oâ€™clock in the morning, until 9 at night in</t>
+          <t>L649: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: dividual taking it•</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å�£</t>
+          <t>L86: stray/suspicious non-ASCII glyph(s): U+53E3 CJK UNIFIED IDEOGRAPH-53E3 | isolated marker/symbol line :: 口</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
@@ -1652,13 +1656,13 @@
       <c r="P14" s="1" t="inlineStr"/>
       <c r="Q14" s="1" t="inlineStr">
         <is>
-          <t>L517: punctuation artifact: repeated periods :: ing the larger sizes..</t>
+          <t>L671: punctuation artifact: repeated periods :: [Medicine .. It will press the obligations I am under for the entire</t>
         </is>
       </c>
       <c r="R14" s="1" t="inlineStr"/>
       <c r="S14" s="1" t="inlineStr">
         <is>
-          <t>L1124: line starts with digit/letter garbage token | suspicious token(s): 1Wholesale (letter/digit mix) :: 1Wholesale and for Exportation by the</t>
+          <t>L591: line starts with punctuation glued to text :: .Dysentery. Dropsy</t>
         </is>
       </c>
       <c r="T14" s="1" t="inlineStr"/>
@@ -1704,12 +1708,12 @@
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>L726: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: pr Ã© es ths obligations I om under for tbe entire</t>
+          <t>L863: stray/suspicious non-ASCII glyph(s): U+4E14 CJK UNIFIED IDEOGRAPH-4E14, U+65E5 CJK UNIFIED IDEOGRAPH-65E5 :: 且 日</t>
         </is>
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>L230: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: _â€” ______________- ----------------â€” The treatment they adopt is the result of</t>
+          <t>L652: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: gently on the Bowel- ©</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr"/>
@@ -1721,17 +1725,21 @@
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L854: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L854: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
       <c r="Q15" s="1" t="inlineStr">
         <is>
-          <t>L671: punctuation artifact: repeated periods :: [Medicine .. It will press the obligations I am under for the entire</t>
+          <t>L719: punctuation artifact: repeated periods :: Solicitor.........- Angus Morrison, Esq.</t>
         </is>
       </c>
       <c r="R15" s="1" t="inlineStr"/>
-      <c r="S15" s="1" t="inlineStr"/>
+      <c r="S15" s="1" t="inlineStr">
+        <is>
+          <t>L599: line starts with digit/letter garbage token | suspicious token(s): 1Morbus (letter/digit mix) :: 1Morbus, I give it to you at the request of Mr Bradford</t>
+        </is>
+      </c>
       <c r="T15" s="1" t="inlineStr"/>
       <c r="U15" s="1" t="inlineStr"/>
       <c r="V15" s="1" t="inlineStr"/>
@@ -1775,12 +1783,12 @@
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>L771: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L902: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>L232: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: CAN ADA upwards of 30 yearsâ€™ extensive and and sue</t>
+          <t>L673: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN :: ™ thousands can about the time of my arrival in the United</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr"/>
@@ -1798,11 +1806,15 @@
       <c r="P16" s="1" t="inlineStr"/>
       <c r="Q16" s="1" t="inlineStr">
         <is>
-          <t>L719: punctuation artifact: repeated periods :: Solicitor.........- Angus Morrison, Esq.</t>
+          <t>L721: punctuation artifact: repeated periods :: Bankers.............BANK UP. CANADA</t>
         </is>
       </c>
       <c r="R16" s="1" t="inlineStr"/>
-      <c r="S16" s="1" t="inlineStr"/>
+      <c r="S16" s="1" t="inlineStr">
+        <is>
+          <t>L644: line starts with punctuation glued to text :: .tifiestesin my pos</t>
+        </is>
+      </c>
       <c r="T16" s="1" t="inlineStr"/>
       <c r="U16" s="1" t="inlineStr"/>
       <c r="V16" s="1" t="inlineStr"/>
@@ -1846,12 +1858,12 @@
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
-          <t>L833: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L917: stray/suspicious non-ASCII glyph(s): U+2265 GREATER-THAN OR EQUAL TO | isolated marker/symbol line :: ≥</t>
         </is>
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>L276: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: tedâ€” inst loss or damage - A CURE WARRANTED- for their use in the following co maiserder</t>
+          <t>L700: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: • • Sold at the Manufactories of Professor</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr"/>
@@ -1869,11 +1881,15 @@
       <c r="P17" s="1" t="inlineStr"/>
       <c r="Q17" s="1" t="inlineStr">
         <is>
-          <t>L721: punctuation artifact: repeated periods :: Bankers.............BANK UP. CANADA</t>
+          <t>L734: punctuation artifact: double/multiple hyphen :: e ------------------------ - - cures and directions</t>
         </is>
       </c>
       <c r="R17" s="1" t="inlineStr"/>
-      <c r="S17" s="1" t="inlineStr"/>
+      <c r="S17" s="1" t="inlineStr">
+        <is>
+          <t>L842: line starts with punctuation glued to text :: .w high all express in ly. if neglected, end which have now stood the test of public exp-</t>
+        </is>
+      </c>
       <c r="T17" s="1" t="inlineStr"/>
       <c r="U17" s="1" t="inlineStr"/>
       <c r="V17" s="1" t="inlineStr"/>
@@ -1895,7 +1911,7 @@
       <c r="G18" s="1" t="inlineStr"/>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>L457: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): m0s (letter/digit mix) :: m0sâ€ skeptical as to the merits of their in-</t>
+          <t>L457: suspicious token(s): m0s (letter/digit mix) :: m0s† skeptical as to the merits of their in-</t>
         </is>
       </c>
       <c r="I18" s="1" t="inlineStr">
@@ -1905,12 +1921,12 @@
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>L863: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00A5 YEN SIGN :: ä¸” æ—¥</t>
+          <t>L950: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>L285: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢information to be had on applying at the complaints, or from whom genuine European , ALICE Tell</t>
+          <t>L706: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: are so composed that disease within the range ©-</t>
         </is>
       </c>
       <c r="L18" s="1" t="inlineStr"/>
@@ -1928,11 +1944,15 @@
       <c r="P18" s="1" t="inlineStr"/>
       <c r="Q18" s="1" t="inlineStr">
         <is>
-          <t>L734: punctuation artifact: double/multiple hyphen :: e ------------------------ - - cures and directions</t>
+          <t>L840: punctuation artifact: double/multiple hyphen | suspicious token(s): Filma63 (letter/digit mix) :: -toneused the Filma63--a</t>
         </is>
       </c>
       <c r="R18" s="1" t="inlineStr"/>
-      <c r="S18" s="1" t="inlineStr"/>
+      <c r="S18" s="1" t="inlineStr">
+        <is>
+          <t>L1124: line starts with digit/letter garbage token | suspicious token(s): 1Wholesale (letter/digit mix) :: 1Wholesale and for Exportation by the</t>
+        </is>
+      </c>
       <c r="T18" s="1" t="inlineStr"/>
       <c r="U18" s="1" t="inlineStr"/>
       <c r="V18" s="1" t="inlineStr"/>
@@ -1964,12 +1984,12 @@
       </c>
       <c r="J19" s="1" t="inlineStr">
         <is>
-          <t>L899: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): A1901 (letter/digit mix) :: â€” A1901</t>
+          <t>L966: stray/suspicious non-ASCII glyph(s): U+FF01 FULLWIDTH EXCLAMATION MARK | isolated marker/symbol line :: ！</t>
         </is>
       </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>L289: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: 1. C HART, Persons IN ANY PART OF THE WORLD â€¢ of -----</t>
+          <t>L791: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="L19" s="1" t="inlineStr"/>
@@ -1987,7 +2007,7 @@
       <c r="P19" s="1" t="inlineStr"/>
       <c r="Q19" s="1" t="inlineStr">
         <is>
-          <t>L840: punctuation artifact: double/multiple hyphen | suspicious token(s): Filma63 (letter/digit mix) :: -toneused the Filma63--a</t>
+          <t>L912: punctuation artifact: repeated periods | missing space around punctuation :: .-.... teething, by softening the gums,reducing</t>
         </is>
       </c>
       <c r="R19" s="1" t="inlineStr"/>
@@ -2023,12 +2043,12 @@
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
-          <t>L902: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L1047: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K20" s="1" t="inlineStr">
         <is>
-          <t>L292: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | line starts with punctuation glued to text :: _________________________â€” â€” correct detail of their cases witha remit-</t>
+          <t>L854: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L20" s="1" t="inlineStr"/>
@@ -2046,7 +2066,7 @@
       <c r="P20" s="1" t="inlineStr"/>
       <c r="Q20" s="1" t="inlineStr">
         <is>
-          <t>L912: punctuation artifact: repeated periods | missing space around punctuation :: .-.... teething, by softening the gums,reducing</t>
+          <t>L916: punctuation artifact: repeated periods | suspicious token(s): theirSAUCE (odd internal casing) :: theirSAUCE is, LATE THE BOWELS..</t>
         </is>
       </c>
       <c r="R20" s="1" t="inlineStr"/>
@@ -2082,12 +2102,12 @@
       </c>
       <c r="J21" s="1" t="inlineStr">
         <is>
-          <t>L917: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: â‰¥</t>
+          <t>L1119: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: c ：</t>
         </is>
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>L334: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: every countryâ€”a record, the like</t>
+          <t>L886: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: use. When once tried, its superiority over €</t>
         </is>
       </c>
       <c r="L21" s="1" t="inlineStr"/>
@@ -2105,7 +2125,7 @@
       <c r="P21" s="1" t="inlineStr"/>
       <c r="Q21" s="1" t="inlineStr">
         <is>
-          <t>L916: punctuation artifact: repeated periods | suspicious token(s): theirSAUCE (odd internal casing) :: theirSAUCE is, LATE THE BOWELS..</t>
+          <t>L934: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: well know that diffe- •</t>
         </is>
       </c>
       <c r="R21" s="1" t="inlineStr"/>
@@ -2136,17 +2156,17 @@
       </c>
       <c r="I22" s="1" t="inlineStr">
         <is>
-          <t>L675: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE, U+2122 TRADE MARK SIGN, U+FFFD REPLACEMENT CHARACTER | suspicious token(s): HalfRestorative (odd internal casing) :: minutes, if two or on the application ofâ€˜ourâ€™ HalfRestorativeâ€�</t>
+          <t>L675: suspicious token(s): HalfRestorative (odd internal casing) :: minutes, if two or on the application of‘our’ HalfRestorative”</t>
         </is>
       </c>
       <c r="J22" s="1" t="inlineStr">
         <is>
-          <t>L950: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L1191: stray/suspicious non-ASCII glyph(s): U+5EFA CJK UNIFIED IDEOGRAPH-5EFA | isolated marker/symbol line :: 建</t>
         </is>
       </c>
       <c r="K22" s="1" t="inlineStr">
         <is>
-          <t>L354: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: cimatest. Suman family has its origin directly don.â€� are discernable as a Water mark in</t>
+          <t>L929: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: DR. J. €. AVER &amp; Co.</t>
         </is>
       </c>
       <c r="L22" s="1" t="inlineStr"/>
@@ -2164,7 +2184,7 @@
       <c r="P22" s="1" t="inlineStr"/>
       <c r="Q22" s="1" t="inlineStr">
         <is>
-          <t>L966: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: hyphen/bullet debris :: â€” â€” -**. DYSPEPSIA â€”No person with this distress-</t>
+          <t>L966: punctuation artifact: hyphen/bullet debris :: — — -**. DYSPEPSIA —No person with this distress-</t>
         </is>
       </c>
       <c r="R22" s="1" t="inlineStr"/>
@@ -2200,12 +2220,12 @@
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
-          <t>L960: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: t Incorporate â€œThe College of Three</t>
+          <t>L1192: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K23" s="1" t="inlineStr">
         <is>
-          <t>L367: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: Such a medicine we supply in - -----â€”â€”</t>
+          <t>L934: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: well know that diffe- •</t>
         </is>
       </c>
       <c r="L23" s="1" t="inlineStr"/>
@@ -2259,12 +2279,12 @@
       </c>
       <c r="J24" s="1" t="inlineStr">
         <is>
-          <t>L966: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: ï¼�</t>
+          <t>L1194: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="K24" s="1" t="inlineStr">
         <is>
-          <t>L369: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: AYERâ€™S</t>
+          <t>L940: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): thartiePill (odd internal casing) | missing space around punctuation :: thartiePill has,with © Rheumatism, a great | I London. Sold retail by all Druggists and Pa-</t>
         </is>
       </c>
       <c r="L24" s="1" t="inlineStr"/>
@@ -2318,12 +2338,12 @@
       </c>
       <c r="J25" s="1" t="inlineStr">
         <is>
-          <t>L1020: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ABSOLUTELY SURE â€” to follow the use of</t>
+          <t>L1305: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K25" s="1" t="inlineStr">
         <is>
-          <t>L390: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1345: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L25" s="1" t="inlineStr"/>
@@ -2377,14 +2397,10 @@
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
-          <t>L1121: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Tob CONSUMPTIVES â€” TENT.</t>
-        </is>
-      </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L398: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ YS</t>
-        </is>
-      </c>
+          <t>L1308: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
@@ -2434,21 +2450,13 @@
           <t>L916: punctuation artifact: repeated periods | suspicious token(s): theirSAUCE (odd internal casing) :: theirSAUCE is, LATE THE BOWELS..</t>
         </is>
       </c>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>L1192: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L424: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: it from the patientâ€™s system,</t>
-        </is>
-      </c>
+      <c r="J27" s="1" t="inlineStr"/>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L287: isolated marker/symbol line :: H</t>
+          <t>L286: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
@@ -2459,7 +2467,7 @@
       <c r="P27" s="1" t="inlineStr"/>
       <c r="Q27" s="1" t="inlineStr">
         <is>
-          <t>L1204: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: â€” anxious to make known to his fellow-suf- _______â€” ......</t>
+          <t>L1204: punctuation artifact: repeated periods :: — anxious to make known to his fellow-suf- _______— ......</t>
         </is>
       </c>
       <c r="R27" s="1" t="inlineStr"/>
@@ -2490,24 +2498,16 @@
       </c>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>L940: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): thartiePill (odd internal casing) | missing space around punctuation :: thartiePill has,with Â© Rheumatism, a great | I London. Sold retail by all Druggists and Pa-</t>
-        </is>
-      </c>
-      <c r="J28" s="1" t="inlineStr">
-        <is>
-          <t>L1223: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Mercurial Diseases. â€” Never fit. to en.</t>
-        </is>
-      </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L442: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Hollowayâ€™s Pills are the best remedy</t>
-        </is>
-      </c>
+          <t>L940: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): thartiePill (odd internal casing) | missing space around punctuation :: thartiePill has,with © Rheumatism, a great | I London. Sold retail by all Druggists and Pa-</t>
+        </is>
+      </c>
+      <c r="J28" s="1" t="inlineStr"/>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L309: isolated marker/symbol line :: U</t>
+          <t>L287: isolated marker/symbol line :: H</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
@@ -2548,21 +2548,13 @@
           <t>L1017: suspicious token(s): 22Notre (letter/digit mix) :: 22Notre Dame Street. W. LAMB Me-</t>
         </is>
       </c>
-      <c r="J29" s="1" t="inlineStr">
-        <is>
-          <t>L1308: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L443: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: known in the world for theâ€¢</t>
-        </is>
-      </c>
+      <c r="J29" s="1" t="inlineStr"/>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L311: isolated marker/symbol line :: 6</t>
+          <t>L304: stray/suspicious non-ASCII glyph(s): U+4E0A CJK UNIFIED IDEOGRAPH-4E0A | isolated marker/symbol line :: 上</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
@@ -2604,16 +2596,12 @@
         </is>
       </c>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L506: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+2122 TRADE MARK SIGN :: â€¢ Hair Restorativeâ€™ which he liked very much</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L312: isolated marker/symbol line :: 4</t>
+          <t>L309: isolated marker/symbol line :: U</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
@@ -2655,16 +2643,12 @@
         </is>
       </c>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L556: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: and SKIN DISEASES, Sr. ANTHONYâ€™S FIRE,</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L334: isolated marker/symbol line :: 4</t>
+          <t>L311: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
@@ -2706,21 +2690,17 @@
         </is>
       </c>
       <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L569: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Fever &amp; Ague.â€”</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L335: isolated marker/symbol line :: 1</t>
+          <t>L312: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L1345: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1345: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -2757,16 +2737,12 @@
         </is>
       </c>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L601: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: â‚¬holers Infantum You can sell a great deal of your Hair Resto-</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L336: isolated marker/symbol line :: A</t>
+          <t>L334: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
@@ -2804,16 +2780,12 @@
         </is>
       </c>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L607: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: in ** impurity of the bloodâ€� is founded m</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L337: isolated marker/symbol line :: 8</t>
+          <t>L335: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
@@ -2847,20 +2819,16 @@
       </c>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>L1292: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): SEALdo (odd internal casing) :: U PALE SEALdo.â€” 25 barrels very fine,</t>
+          <t>L1292: suspicious token(s): SEALdo (odd internal casing) :: U PALE SEALdo.— 25 barrels very fine,</t>
         </is>
       </c>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L618: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: F CAUTION â€” None are genuine unless</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L338: isolated marker/symbol line :: S</t>
+          <t>L336: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
@@ -2898,16 +2866,12 @@
         </is>
       </c>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L645: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Ayerâ€™s Cathartic Pills, dose must be</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L339: isolated marker/symbol line :: 1</t>
+          <t>L337: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
@@ -2936,21 +2900,17 @@
       <c r="G37" s="1" t="inlineStr"/>
       <c r="H37" s="1" t="inlineStr">
         <is>
-          <t>L899: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): A1901 (letter/digit mix) :: â€” A1901</t>
+          <t>L899: suspicious token(s): A1901 (letter/digit mix) :: — A1901</t>
         </is>
       </c>
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L649: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: dividual taking itâ€¢</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L340: isolated marker/symbol line :: 0</t>
+          <t>L338: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
@@ -2984,16 +2944,12 @@
       </c>
       <c r="I38" s="1" t="inlineStr"/>
       <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L652: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: gently on the Bowel- Â©</t>
-        </is>
-      </c>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L341: isolated marker/symbol line :: x</t>
+          <t>L339: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
@@ -3027,16 +2983,12 @@
       </c>
       <c r="I39" s="1" t="inlineStr"/>
       <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L673: stray/suspicious non-ASCII glyph(s): U+00A2 CENT SIGN :: â„¢ thousands can about the time of my arrival in the United</t>
-        </is>
-      </c>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L342: symbol-only separator/garbage line :: $3 00</t>
+          <t>L340: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr"/>
@@ -3066,16 +3018,12 @@
       </c>
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L675: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE, U+2122 TRADE MARK SIGN, U+FFFD REPLACEMENT CHARACTER | suspicious token(s): HalfRestorative (odd internal casing) :: minutes, if two or on the application ofâ€˜ourâ€™ HalfRestorativeâ€�</t>
-        </is>
-      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L343: isolated marker/symbol line :: 300</t>
+          <t>L341: isolated marker/symbol line :: x</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr"/>
@@ -3105,16 +3053,12 @@
       </c>
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L700: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ â€¢ Sold at the Manufactories of Professor</t>
-        </is>
-      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L344: symbol-only separator/garbage line :: 5 00</t>
+          <t>L342: symbol-only separator/garbage line :: $3 00</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr"/>
@@ -3144,16 +3088,12 @@
       </c>
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L706: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: are so composed that disease within the range Â©-</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L345: isolated marker/symbol line :: y</t>
+          <t>L343: isolated marker/symbol line :: 300</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr"/>
@@ -3183,16 +3123,12 @@
       </c>
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L750: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: N B â€” Directions for the guidance of pa-</t>
-        </is>
-      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L346: isolated marker/symbol line :: 700</t>
+          <t>L344: symbol-only separator/garbage line :: 5 00</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr"/>
@@ -3222,16 +3158,12 @@
       </c>
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L791: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L347: isolated marker/symbol line :: 900</t>
+          <t>L345: isolated marker/symbol line :: y</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr"/>
@@ -3261,16 +3193,12 @@
       </c>
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L793: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: MOFFATâ€™S</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L348: isolated marker/symbol line :: m</t>
+          <t>L346: isolated marker/symbol line :: 700</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr"/>
@@ -3300,16 +3228,12 @@
       </c>
       <c r="I46" s="1" t="inlineStr"/>
       <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L826: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: KEATINGâ€™S</t>
-        </is>
-      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L351: isolated marker/symbol line :: 9</t>
+          <t>L347: isolated marker/symbol line :: 900</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr"/>
@@ -3339,16 +3263,12 @@
       </c>
       <c r="I47" s="1" t="inlineStr"/>
       <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L839: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: I creasing demand / ness. Pain and Sore and other constitutic naâ€˜ derangements. The</t>
-        </is>
-      </c>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L352: isolated marker/symbol line :: P.</t>
+          <t>L348: isolated marker/symbol line :: m</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr"/>
@@ -3378,16 +3298,12 @@
       </c>
       <c r="I48" s="1" t="inlineStr"/>
       <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L854: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L367: isolated marker/symbol line :: 000</t>
+          <t>L350: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr"/>
@@ -3417,16 +3333,12 @@
       </c>
       <c r="I49" s="1" t="inlineStr"/>
       <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L878: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Complaints.â€”la the south and west, where</t>
-        </is>
-      </c>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L369: isolated marker/symbol line :: 0</t>
+          <t>L351: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr"/>
@@ -3456,16 +3368,12 @@
       </c>
       <c r="I50" s="1" t="inlineStr"/>
       <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L886: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: use. When once tried, its superiority over â‚¬</t>
-        </is>
-      </c>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L370: symbol-only separator/garbage line :: $400, 000.</t>
+          <t>L352: isolated marker/symbol line :: P.</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr"/>
@@ -3495,16 +3403,12 @@
       </c>
       <c r="I51" s="1" t="inlineStr"/>
       <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L914: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Tell LEA &amp; all inflammationâ€”will allay ALL PAIN and</t>
-        </is>
-      </c>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L374: isolated marker/symbol line :: è£…</t>
+          <t>L367: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr"/>
@@ -3534,16 +3438,12 @@
       </c>
       <c r="I52" s="1" t="inlineStr"/>
       <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L929: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: DR. J. â‚¬. AVER &amp; Co.</t>
-        </is>
-      </c>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L375: isolated marker/symbol line :: %</t>
+          <t>L369: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr"/>
@@ -3573,16 +3473,12 @@
       </c>
       <c r="I53" s="1" t="inlineStr"/>
       <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L934: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: well know that diffe- â€¢</t>
-        </is>
-      </c>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L381: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L370: symbol-only separator/garbage line :: $400, 000.</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr"/>
@@ -3612,16 +3508,12 @@
       </c>
       <c r="I54" s="1" t="inlineStr"/>
       <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L939: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: The Family Ca E Children or Adults, mist &amp;c. No. 19. St. Paulâ€™s Church Yard,</t>
-        </is>
-      </c>
+      <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L383: isolated marker/symbol line :: .</t>
+          <t>L374: stray/suspicious non-ASCII glyph(s): U+88C5 CJK UNIFIED IDEOGRAPH-88C5 | isolated marker/symbol line :: 装</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr"/>
@@ -3651,16 +3543,12 @@
       </c>
       <c r="I55" s="1" t="inlineStr"/>
       <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L940: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): thartiePill (odd internal casing) | missing space around punctuation :: thartiePill has,with Â© Rheumatism, a great | I London. Sold retail by all Druggists and Pa-</t>
-        </is>
-      </c>
+      <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L409: isolated marker/symbol line :: .</t>
+          <t>L375: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr"/>
@@ -3690,16 +3578,12 @@
       </c>
       <c r="I56" s="1" t="inlineStr"/>
       <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L942: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: well established fact, and many diseases to N. B â€”To prevent spurious imitations</t>
-        </is>
-      </c>
+      <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L424: symbol-only separator/garbage line :: 1851.</t>
+          <t>L381: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr"/>
@@ -3729,16 +3613,12 @@
       </c>
       <c r="I57" s="1" t="inlineStr"/>
       <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L944: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: been compounded which Beth isheir, please observe that the words, KEATINGâ€™S</t>
-        </is>
-      </c>
+      <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L430: isolated marker/symbol line :: A</t>
+          <t>L383: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr"/>
@@ -3768,16 +3648,12 @@
       </c>
       <c r="I58" s="1" t="inlineStr"/>
       <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L966: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: hyphen/bullet debris :: â€” â€” -**. DYSPEPSIA â€”No person with this distress-</t>
-        </is>
-      </c>
+      <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L467: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L409: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr"/>
@@ -3807,16 +3683,12 @@
       </c>
       <c r="I59" s="1" t="inlineStr"/>
       <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L982: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” WORCESTERSHIRE SAUCE," the la-</t>
-        </is>
-      </c>
+      <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L514: isolated marker/symbol line :: 0</t>
+          <t>L424: symbol-only separator/garbage line :: 1851.</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr"/>
@@ -3846,16 +3718,12 @@
       </c>
       <c r="I60" s="1" t="inlineStr"/>
       <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L993: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Ladiesâ€™</t>
-        </is>
-      </c>
+      <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L527: isolated marker/symbol line :: P</t>
+          <t>L430: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr"/>
@@ -3885,16 +3753,12 @@
       </c>
       <c r="I61" s="1" t="inlineStr"/>
       <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L1007: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: system subject to a return of the diseaseâ€”</t>
-        </is>
-      </c>
+      <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L528: isolated marker/symbol line :: y</t>
+          <t>L467: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr"/>
@@ -3924,16 +3788,12 @@
       </c>
       <c r="I62" s="1" t="inlineStr"/>
       <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L1008: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: a cure by these medicines is permanent.â€”</t>
-        </is>
-      </c>
+      <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L559: isolated marker/symbol line :: 7</t>
+          <t>L514: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr"/>
@@ -3963,16 +3823,12 @@
       </c>
       <c r="I63" s="1" t="inlineStr"/>
       <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L1011: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: MERCURAL DISEASES â€”Never fails to era-</t>
-        </is>
-      </c>
+      <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L565: isolated marker/symbol line :: 1</t>
+          <t>L527: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr"/>
@@ -3997,21 +3853,17 @@
       <c r="G64" s="1" t="inlineStr"/>
       <c r="H64" s="1" t="inlineStr">
         <is>
-          <t>L1205: suspicious token(s): CAsEs (odd internal casing) :: Â· IN ALL CAsEs OP Asthma, Aeste and</t>
+          <t>L1205: suspicious token(s): CAsEs (odd internal casing) :: · IN ALL CAsEs OP Asthma, Aeste and</t>
         </is>
       </c>
       <c r="I64" s="1" t="inlineStr"/>
       <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L1028: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: of Keelingâ€™s Cough Lozenges is re-</t>
-        </is>
-      </c>
+      <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L576: isolated marker/symbol line :: *</t>
+          <t>L528: isolated marker/symbol line :: y</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr"/>
@@ -4041,16 +3893,12 @@
       </c>
       <c r="I65" s="1" t="inlineStr"/>
       <c r="J65" s="1" t="inlineStr"/>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>L1041: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: No. I Gibâ€™</t>
-        </is>
-      </c>
+      <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L577: isolated marker/symbol line :: t</t>
+          <t>L559: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr"/>
@@ -4080,16 +3928,12 @@
       </c>
       <c r="I66" s="1" t="inlineStr"/>
       <c r="J66" s="1" t="inlineStr"/>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>L1092: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: SIR.â€”Thevery excellent properties of your</t>
-        </is>
-      </c>
+      <c r="K66" s="1" t="inlineStr"/>
       <c r="L66" s="1" t="inlineStr"/>
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L588: isolated marker/symbol line :: .</t>
+          <t>L565: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr"/>
@@ -4119,16 +3963,12 @@
       </c>
       <c r="I67" s="1" t="inlineStr"/>
       <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>L1099: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Palpitation of the Heart, Painterâ€™s Cholic.</t>
-        </is>
-      </c>
+      <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L595: isolated marker/symbol line :: T</t>
+          <t>L576: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr"/>
@@ -4158,16 +3998,12 @@
       </c>
       <c r="I68" s="1" t="inlineStr"/>
       <c r="J68" s="1" t="inlineStr"/>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>L1101: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: PILES â€”The original Proprietor of these</t>
-        </is>
-      </c>
+      <c r="K68" s="1" t="inlineStr"/>
       <c r="L68" s="1" t="inlineStr"/>
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L596: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L577: isolated marker/symbol line :: t</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr"/>
@@ -4197,16 +4033,12 @@
       </c>
       <c r="I69" s="1" t="inlineStr"/>
       <c r="J69" s="1" t="inlineStr"/>
-      <c r="K69" s="1" t="inlineStr">
-        <is>
-          <t>L1116: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: yoursâ€”even one of them will check the most</t>
-        </is>
-      </c>
+      <c r="K69" s="1" t="inlineStr"/>
       <c r="L69" s="1" t="inlineStr"/>
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L635: isolated marker/symbol line :: 1</t>
+          <t>L588: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr"/>
@@ -4236,16 +4068,12 @@
       </c>
       <c r="I70" s="1" t="inlineStr"/>
       <c r="J70" s="1" t="inlineStr"/>
-      <c r="K70" s="1" t="inlineStr">
-        <is>
-          <t>L1148: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: TO CONSUMPTIVES â€” The advertiser</t>
-        </is>
-      </c>
+      <c r="K70" s="1" t="inlineStr"/>
       <c r="L70" s="1" t="inlineStr"/>
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L636: isolated marker/symbol line :: 10</t>
+          <t>L595: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr"/>
@@ -4275,16 +4103,12 @@
       </c>
       <c r="I71" s="1" t="inlineStr"/>
       <c r="J71" s="1" t="inlineStr"/>
-      <c r="K71" s="1" t="inlineStr">
-        <is>
-          <t>L1204: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: â€” anxious to make known to his fellow-suf- _______â€” ......</t>
-        </is>
-      </c>
+      <c r="K71" s="1" t="inlineStr"/>
       <c r="L71" s="1" t="inlineStr"/>
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>L645: isolated marker/symbol line :: 4</t>
+          <t>L596: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr"/>
@@ -4314,16 +4138,12 @@
       </c>
       <c r="I72" s="1" t="inlineStr"/>
       <c r="J72" s="1" t="inlineStr"/>
-      <c r="K72" s="1" t="inlineStr">
-        <is>
-          <t>L1291: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ASPE COD OILâ€”100 bbls. Ex. Choice.</t>
-        </is>
-      </c>
+      <c r="K72" s="1" t="inlineStr"/>
       <c r="L72" s="1" t="inlineStr"/>
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>L723: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L635: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr"/>
@@ -4353,16 +4173,12 @@
       </c>
       <c r="I73" s="1" t="inlineStr"/>
       <c r="J73" s="1" t="inlineStr"/>
-      <c r="K73" s="1" t="inlineStr">
-        <is>
-          <t>L1292: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): SEALdo (odd internal casing) :: U PALE SEALdo.â€” 25 barrels very fine,</t>
-        </is>
-      </c>
+      <c r="K73" s="1" t="inlineStr"/>
       <c r="L73" s="1" t="inlineStr"/>
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>L731: isolated marker/symbol line :: -</t>
+          <t>L636: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr"/>
@@ -4388,16 +4204,12 @@
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr"/>
       <c r="J74" s="1" t="inlineStr"/>
-      <c r="K74" s="1" t="inlineStr">
-        <is>
-          <t>L1310: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: lug child and the relief will be SUREâ€”yes.</t>
-        </is>
-      </c>
+      <c r="K74" s="1" t="inlineStr"/>
       <c r="L74" s="1" t="inlineStr"/>
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t>L735: isolated marker/symbol line :: 4</t>
+          <t>L645: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr"/>
@@ -4423,16 +4235,12 @@
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr"/>
       <c r="J75" s="1" t="inlineStr"/>
-      <c r="K75" s="1" t="inlineStr">
-        <is>
-          <t>L1311: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ABSOLUTELY SUREâ€”to follow the use of</t>
-        </is>
-      </c>
+      <c r="K75" s="1" t="inlineStr"/>
       <c r="L75" s="1" t="inlineStr"/>
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>L770: isolated marker/symbol line :: A</t>
+          <t>L723: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr"/>
@@ -4458,16 +4266,12 @@
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr"/>
       <c r="J76" s="1" t="inlineStr"/>
-      <c r="K76" s="1" t="inlineStr">
-        <is>
-          <t>L1329: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: Nâ€œ Scottsâ€� Brand, Choice,</t>
-        </is>
-      </c>
+      <c r="K76" s="1" t="inlineStr"/>
       <c r="L76" s="1" t="inlineStr"/>
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr">
         <is>
-          <t>L771: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L731: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O76" s="1" t="inlineStr"/>
@@ -4493,16 +4297,12 @@
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr"/>
       <c r="J77" s="1" t="inlineStr"/>
-      <c r="K77" s="1" t="inlineStr">
-        <is>
-          <t>L1334: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: GENERAL ASSORTMENT.â€”For Sale</t>
-        </is>
-      </c>
+      <c r="K77" s="1" t="inlineStr"/>
       <c r="L77" s="1" t="inlineStr"/>
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr">
         <is>
-          <t>L802: isolated marker/symbol line :: P</t>
+          <t>L735: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O77" s="1" t="inlineStr"/>
@@ -4528,16 +4328,12 @@
       <c r="H78" s="1" t="inlineStr"/>
       <c r="I78" s="1" t="inlineStr"/>
       <c r="J78" s="1" t="inlineStr"/>
-      <c r="K78" s="1" t="inlineStr">
-        <is>
-          <t>L1340: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: DVASS,â€”</t>
-        </is>
-      </c>
+      <c r="K78" s="1" t="inlineStr"/>
       <c r="L78" s="1" t="inlineStr"/>
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr">
         <is>
-          <t>L833: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L748: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O78" s="1" t="inlineStr"/>
@@ -4563,16 +4359,12 @@
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr"/>
       <c r="J79" s="1" t="inlineStr"/>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>L1345: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K79" s="1" t="inlineStr"/>
       <c r="L79" s="1" t="inlineStr"/>
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr">
         <is>
-          <t>L834: isolated marker/symbol line :: 7</t>
+          <t>L770: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O79" s="1" t="inlineStr"/>
@@ -4603,7 +4395,7 @@
       <c r="M80" s="1" t="inlineStr"/>
       <c r="N80" s="1" t="inlineStr">
         <is>
-          <t>L850: isolated marker/symbol line :: 2</t>
+          <t>L771: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O80" s="1" t="inlineStr"/>
@@ -4634,7 +4426,7 @@
       <c r="M81" s="1" t="inlineStr"/>
       <c r="N81" s="1" t="inlineStr">
         <is>
-          <t>L882: isolated marker/symbol line :: H</t>
+          <t>L802: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="O81" s="1" t="inlineStr"/>
@@ -4665,7 +4457,7 @@
       <c r="M82" s="1" t="inlineStr"/>
       <c r="N82" s="1" t="inlineStr">
         <is>
-          <t>L891: isolated marker/symbol line :: .</t>
+          <t>L833: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="O82" s="1" t="inlineStr"/>
@@ -4696,7 +4488,7 @@
       <c r="M83" s="1" t="inlineStr"/>
       <c r="N83" s="1" t="inlineStr">
         <is>
-          <t>L892: isolated marker/symbol line :: X</t>
+          <t>L834: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O83" s="1" t="inlineStr"/>
@@ -4727,7 +4519,7 @@
       <c r="M84" s="1" t="inlineStr"/>
       <c r="N84" s="1" t="inlineStr">
         <is>
-          <t>L895: isolated marker/symbol line :: 3</t>
+          <t>L850: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O84" s="1" t="inlineStr"/>
@@ -4758,7 +4550,7 @@
       <c r="M85" s="1" t="inlineStr"/>
       <c r="N85" s="1" t="inlineStr">
         <is>
-          <t>L897: isolated marker/symbol line :: 4</t>
+          <t>L882: isolated marker/symbol line :: H</t>
         </is>
       </c>
       <c r="O85" s="1" t="inlineStr"/>
@@ -4789,7 +4581,7 @@
       <c r="M86" s="1" t="inlineStr"/>
       <c r="N86" s="1" t="inlineStr">
         <is>
-          <t>L898: isolated marker/symbol line :: e</t>
+          <t>L891: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O86" s="1" t="inlineStr"/>
@@ -4820,7 +4612,7 @@
       <c r="M87" s="1" t="inlineStr"/>
       <c r="N87" s="1" t="inlineStr">
         <is>
-          <t>L900: isolated marker/symbol line :: 8</t>
+          <t>L892: isolated marker/symbol line :: X</t>
         </is>
       </c>
       <c r="O87" s="1" t="inlineStr"/>
@@ -4851,7 +4643,7 @@
       <c r="M88" s="1" t="inlineStr"/>
       <c r="N88" s="1" t="inlineStr">
         <is>
-          <t>L902: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L895: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O88" s="1" t="inlineStr"/>
@@ -4882,7 +4674,7 @@
       <c r="M89" s="1" t="inlineStr"/>
       <c r="N89" s="1" t="inlineStr">
         <is>
-          <t>L916: isolated marker/symbol line :: C</t>
+          <t>L897: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O89" s="1" t="inlineStr"/>
@@ -4913,7 +4705,7 @@
       <c r="M90" s="1" t="inlineStr"/>
       <c r="N90" s="1" t="inlineStr">
         <is>
-          <t>L917: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: â‰¥</t>
+          <t>L898: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="O90" s="1" t="inlineStr"/>
@@ -4944,7 +4736,7 @@
       <c r="M91" s="1" t="inlineStr"/>
       <c r="N91" s="1" t="inlineStr">
         <is>
-          <t>L919: isolated marker/symbol line :: e</t>
+          <t>L900: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O91" s="1" t="inlineStr"/>
@@ -4975,7 +4767,7 @@
       <c r="M92" s="1" t="inlineStr"/>
       <c r="N92" s="1" t="inlineStr">
         <is>
-          <t>L923: isolated marker/symbol line :: L.</t>
+          <t>L902: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="O92" s="1" t="inlineStr"/>
@@ -5006,7 +4798,7 @@
       <c r="M93" s="1" t="inlineStr"/>
       <c r="N93" s="1" t="inlineStr">
         <is>
-          <t>L934: isolated marker/symbol line :: N</t>
+          <t>L916: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="O93" s="1" t="inlineStr"/>
@@ -5037,7 +4829,7 @@
       <c r="M94" s="1" t="inlineStr"/>
       <c r="N94" s="1" t="inlineStr">
         <is>
-          <t>L949: isolated marker/symbol line :: 2</t>
+          <t>L917: stray/suspicious non-ASCII glyph(s): U+2265 GREATER-THAN OR EQUAL TO | isolated marker/symbol line :: ≥</t>
         </is>
       </c>
       <c r="O94" s="1" t="inlineStr"/>
@@ -5068,7 +4860,7 @@
       <c r="M95" s="1" t="inlineStr"/>
       <c r="N95" s="1" t="inlineStr">
         <is>
-          <t>L950: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L919: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="O95" s="1" t="inlineStr"/>
@@ -5099,7 +4891,7 @@
       <c r="M96" s="1" t="inlineStr"/>
       <c r="N96" s="1" t="inlineStr">
         <is>
-          <t>L957: isolated marker/symbol line :: 4</t>
+          <t>L923: isolated marker/symbol line :: L.</t>
         </is>
       </c>
       <c r="O96" s="1" t="inlineStr"/>
@@ -5130,7 +4922,7 @@
       <c r="M97" s="1" t="inlineStr"/>
       <c r="N97" s="1" t="inlineStr">
         <is>
-          <t>L965: isolated marker/symbol line :: -</t>
+          <t>L934: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="O97" s="1" t="inlineStr"/>
@@ -5161,7 +4953,7 @@
       <c r="M98" s="1" t="inlineStr"/>
       <c r="N98" s="1" t="inlineStr">
         <is>
-          <t>L983: isolated marker/symbol line :: p</t>
+          <t>L949: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O98" s="1" t="inlineStr"/>
@@ -5192,7 +4984,7 @@
       <c r="M99" s="1" t="inlineStr"/>
       <c r="N99" s="1" t="inlineStr">
         <is>
-          <t>L984: isolated marker/symbol line :: y</t>
+          <t>L950: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O99" s="1" t="inlineStr"/>
@@ -5223,7 +5015,7 @@
       <c r="M100" s="1" t="inlineStr"/>
       <c r="N100" s="1" t="inlineStr">
         <is>
-          <t>L988: isolated marker/symbol line :: f</t>
+          <t>L957: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O100" s="1" t="inlineStr"/>
@@ -5254,7 +5046,7 @@
       <c r="M101" s="1" t="inlineStr"/>
       <c r="N101" s="1" t="inlineStr">
         <is>
-          <t>L989: isolated marker/symbol line :: u</t>
+          <t>L965: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O101" s="1" t="inlineStr"/>
@@ -5285,7 +5077,7 @@
       <c r="M102" s="1" t="inlineStr"/>
       <c r="N102" s="1" t="inlineStr">
         <is>
-          <t>L996: isolated marker/symbol line :: 00</t>
+          <t>L966: stray/suspicious non-ASCII glyph(s): U+FF01 FULLWIDTH EXCLAMATION MARK | isolated marker/symbol line :: ！</t>
         </is>
       </c>
       <c r="O102" s="1" t="inlineStr"/>
@@ -5316,7 +5108,7 @@
       <c r="M103" s="1" t="inlineStr"/>
       <c r="N103" s="1" t="inlineStr">
         <is>
-          <t>L997: isolated marker/symbol line :: a</t>
+          <t>L983: isolated marker/symbol line :: p</t>
         </is>
       </c>
       <c r="O103" s="1" t="inlineStr"/>
@@ -5347,7 +5139,7 @@
       <c r="M104" s="1" t="inlineStr"/>
       <c r="N104" s="1" t="inlineStr">
         <is>
-          <t>L998: isolated marker/symbol line :: .</t>
+          <t>L984: isolated marker/symbol line :: y</t>
         </is>
       </c>
       <c r="O104" s="1" t="inlineStr"/>
@@ -5378,7 +5170,7 @@
       <c r="M105" s="1" t="inlineStr"/>
       <c r="N105" s="1" t="inlineStr">
         <is>
-          <t>L999: isolated marker/symbol line :: o</t>
+          <t>L988: isolated marker/symbol line :: f</t>
         </is>
       </c>
       <c r="O105" s="1" t="inlineStr"/>
@@ -5409,7 +5201,7 @@
       <c r="M106" s="1" t="inlineStr"/>
       <c r="N106" s="1" t="inlineStr">
         <is>
-          <t>L1008: isolated marker/symbol line :: p</t>
+          <t>L989: isolated marker/symbol line :: u</t>
         </is>
       </c>
       <c r="O106" s="1" t="inlineStr"/>
@@ -5440,7 +5232,7 @@
       <c r="M107" s="1" t="inlineStr"/>
       <c r="N107" s="1" t="inlineStr">
         <is>
-          <t>L1017: isolated marker/symbol line :: m</t>
+          <t>L996: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="O107" s="1" t="inlineStr"/>
@@ -5471,7 +5263,7 @@
       <c r="M108" s="1" t="inlineStr"/>
       <c r="N108" s="1" t="inlineStr">
         <is>
-          <t>L1048: isolated marker/symbol line :: 7</t>
+          <t>L997: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="O108" s="1" t="inlineStr"/>
@@ -5502,7 +5294,7 @@
       <c r="M109" s="1" t="inlineStr"/>
       <c r="N109" s="1" t="inlineStr">
         <is>
-          <t>L1089: isolated marker/symbol line :: 0</t>
+          <t>L998: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O109" s="1" t="inlineStr"/>
@@ -5533,7 +5325,7 @@
       <c r="M110" s="1" t="inlineStr"/>
       <c r="N110" s="1" t="inlineStr">
         <is>
-          <t>L1141: isolated marker/symbol line :: A</t>
+          <t>L999: isolated marker/symbol line :: o</t>
         </is>
       </c>
       <c r="O110" s="1" t="inlineStr"/>
@@ -5564,7 +5356,7 @@
       <c r="M111" s="1" t="inlineStr"/>
       <c r="N111" s="1" t="inlineStr">
         <is>
-          <t>L1144: isolated marker/symbol line :: d</t>
+          <t>L1008: isolated marker/symbol line :: p</t>
         </is>
       </c>
       <c r="O111" s="1" t="inlineStr"/>
@@ -5595,7 +5387,7 @@
       <c r="M112" s="1" t="inlineStr"/>
       <c r="N112" s="1" t="inlineStr">
         <is>
-          <t>L1192: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L1017: isolated marker/symbol line :: m</t>
         </is>
       </c>
       <c r="O112" s="1" t="inlineStr"/>
@@ -5626,7 +5418,7 @@
       <c r="M113" s="1" t="inlineStr"/>
       <c r="N113" s="1" t="inlineStr">
         <is>
-          <t>L1193: isolated marker/symbol line :: 1</t>
+          <t>L1047: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O113" s="1" t="inlineStr"/>
@@ -5657,7 +5449,7 @@
       <c r="M114" s="1" t="inlineStr"/>
       <c r="N114" s="1" t="inlineStr">
         <is>
-          <t>L1195: isolated marker/symbol line :: -</t>
+          <t>L1048: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O114" s="1" t="inlineStr"/>
@@ -5688,7 +5480,7 @@
       <c r="M115" s="1" t="inlineStr"/>
       <c r="N115" s="1" t="inlineStr">
         <is>
-          <t>L1196: isolated marker/symbol line :: 2</t>
+          <t>L1089: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O115" s="1" t="inlineStr"/>
@@ -5719,7 +5511,7 @@
       <c r="M116" s="1" t="inlineStr"/>
       <c r="N116" s="1" t="inlineStr">
         <is>
-          <t>L1257: isolated marker/symbol line :: .</t>
+          <t>L1119: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: c ：</t>
         </is>
       </c>
       <c r="O116" s="1" t="inlineStr"/>
@@ -5750,7 +5542,7 @@
       <c r="M117" s="1" t="inlineStr"/>
       <c r="N117" s="1" t="inlineStr">
         <is>
-          <t>L1258: isolated marker/symbol line :: 103</t>
+          <t>L1141: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O117" s="1" t="inlineStr"/>
@@ -5781,7 +5573,7 @@
       <c r="M118" s="1" t="inlineStr"/>
       <c r="N118" s="1" t="inlineStr">
         <is>
-          <t>L1263: isolated marker/symbol line :: 00</t>
+          <t>L1144: isolated marker/symbol line :: d</t>
         </is>
       </c>
       <c r="O118" s="1" t="inlineStr"/>
@@ -5812,7 +5604,7 @@
       <c r="M119" s="1" t="inlineStr"/>
       <c r="N119" s="1" t="inlineStr">
         <is>
-          <t>L1282: isolated marker/symbol line :: W</t>
+          <t>L1191: stray/suspicious non-ASCII glyph(s): U+5EFA CJK UNIFIED IDEOGRAPH-5EFA | isolated marker/symbol line :: 建</t>
         </is>
       </c>
       <c r="O119" s="1" t="inlineStr"/>
@@ -5843,7 +5635,7 @@
       <c r="M120" s="1" t="inlineStr"/>
       <c r="N120" s="1" t="inlineStr">
         <is>
-          <t>L1297: isolated marker/symbol line :: 4</t>
+          <t>L1192: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O120" s="1" t="inlineStr"/>
@@ -5874,7 +5666,7 @@
       <c r="M121" s="1" t="inlineStr"/>
       <c r="N121" s="1" t="inlineStr">
         <is>
-          <t>L1300: isolated marker/symbol line :: 2</t>
+          <t>L1193: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O121" s="1" t="inlineStr"/>
@@ -5905,7 +5697,7 @@
       <c r="M122" s="1" t="inlineStr"/>
       <c r="N122" s="1" t="inlineStr">
         <is>
-          <t>L1301: isolated marker/symbol line :: D</t>
+          <t>L1194: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="O122" s="1" t="inlineStr"/>
@@ -5936,7 +5728,7 @@
       <c r="M123" s="1" t="inlineStr"/>
       <c r="N123" s="1" t="inlineStr">
         <is>
-          <t>L1302: isolated marker/symbol line :: 0</t>
+          <t>L1195: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O123" s="1" t="inlineStr"/>
@@ -5967,7 +5759,7 @@
       <c r="M124" s="1" t="inlineStr"/>
       <c r="N124" s="1" t="inlineStr">
         <is>
-          <t>L1306: isolated marker/symbol line :: 4</t>
+          <t>L1196: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O124" s="1" t="inlineStr"/>
@@ -5998,7 +5790,7 @@
       <c r="M125" s="1" t="inlineStr"/>
       <c r="N125" s="1" t="inlineStr">
         <is>
-          <t>L1308: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L1257: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O125" s="1" t="inlineStr"/>
@@ -6029,7 +5821,7 @@
       <c r="M126" s="1" t="inlineStr"/>
       <c r="N126" s="1" t="inlineStr">
         <is>
-          <t>L1314: isolated marker/symbol line :: 8</t>
+          <t>L1258: isolated marker/symbol line :: 103</t>
         </is>
       </c>
       <c r="O126" s="1" t="inlineStr"/>
@@ -6060,7 +5852,7 @@
       <c r="M127" s="1" t="inlineStr"/>
       <c r="N127" s="1" t="inlineStr">
         <is>
-          <t>L1317: isolated marker/symbol line :: S</t>
+          <t>L1263: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="O127" s="1" t="inlineStr"/>
@@ -6091,7 +5883,7 @@
       <c r="M128" s="1" t="inlineStr"/>
       <c r="N128" s="1" t="inlineStr">
         <is>
-          <t>L1318: isolated marker/symbol line :: '</t>
+          <t>L1282: isolated marker/symbol line :: W</t>
         </is>
       </c>
       <c r="O128" s="1" t="inlineStr"/>
@@ -6106,6 +5898,316 @@
       <c r="X128" s="1" t="inlineStr"/>
       <c r="Y128" s="1" t="inlineStr"/>
     </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr"/>
+      <c r="B129" s="1" t="inlineStr"/>
+      <c r="C129" s="1" t="inlineStr"/>
+      <c r="D129" s="1" t="inlineStr"/>
+      <c r="E129" s="1" t="inlineStr"/>
+      <c r="F129" s="1" t="inlineStr"/>
+      <c r="G129" s="1" t="inlineStr"/>
+      <c r="H129" s="1" t="inlineStr"/>
+      <c r="I129" s="1" t="inlineStr"/>
+      <c r="J129" s="1" t="inlineStr"/>
+      <c r="K129" s="1" t="inlineStr"/>
+      <c r="L129" s="1" t="inlineStr"/>
+      <c r="M129" s="1" t="inlineStr"/>
+      <c r="N129" s="1" t="inlineStr">
+        <is>
+          <t>L1297: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
+      <c r="O129" s="1" t="inlineStr"/>
+      <c r="P129" s="1" t="inlineStr"/>
+      <c r="Q129" s="1" t="inlineStr"/>
+      <c r="R129" s="1" t="inlineStr"/>
+      <c r="S129" s="1" t="inlineStr"/>
+      <c r="T129" s="1" t="inlineStr"/>
+      <c r="U129" s="1" t="inlineStr"/>
+      <c r="V129" s="1" t="inlineStr"/>
+      <c r="W129" s="1" t="inlineStr"/>
+      <c r="X129" s="1" t="inlineStr"/>
+      <c r="Y129" s="1" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr"/>
+      <c r="B130" s="1" t="inlineStr"/>
+      <c r="C130" s="1" t="inlineStr"/>
+      <c r="D130" s="1" t="inlineStr"/>
+      <c r="E130" s="1" t="inlineStr"/>
+      <c r="F130" s="1" t="inlineStr"/>
+      <c r="G130" s="1" t="inlineStr"/>
+      <c r="H130" s="1" t="inlineStr"/>
+      <c r="I130" s="1" t="inlineStr"/>
+      <c r="J130" s="1" t="inlineStr"/>
+      <c r="K130" s="1" t="inlineStr"/>
+      <c r="L130" s="1" t="inlineStr"/>
+      <c r="M130" s="1" t="inlineStr"/>
+      <c r="N130" s="1" t="inlineStr">
+        <is>
+          <t>L1300: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
+      <c r="O130" s="1" t="inlineStr"/>
+      <c r="P130" s="1" t="inlineStr"/>
+      <c r="Q130" s="1" t="inlineStr"/>
+      <c r="R130" s="1" t="inlineStr"/>
+      <c r="S130" s="1" t="inlineStr"/>
+      <c r="T130" s="1" t="inlineStr"/>
+      <c r="U130" s="1" t="inlineStr"/>
+      <c r="V130" s="1" t="inlineStr"/>
+      <c r="W130" s="1" t="inlineStr"/>
+      <c r="X130" s="1" t="inlineStr"/>
+      <c r="Y130" s="1" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr"/>
+      <c r="B131" s="1" t="inlineStr"/>
+      <c r="C131" s="1" t="inlineStr"/>
+      <c r="D131" s="1" t="inlineStr"/>
+      <c r="E131" s="1" t="inlineStr"/>
+      <c r="F131" s="1" t="inlineStr"/>
+      <c r="G131" s="1" t="inlineStr"/>
+      <c r="H131" s="1" t="inlineStr"/>
+      <c r="I131" s="1" t="inlineStr"/>
+      <c r="J131" s="1" t="inlineStr"/>
+      <c r="K131" s="1" t="inlineStr"/>
+      <c r="L131" s="1" t="inlineStr"/>
+      <c r="M131" s="1" t="inlineStr"/>
+      <c r="N131" s="1" t="inlineStr">
+        <is>
+          <t>L1301: isolated marker/symbol line :: D</t>
+        </is>
+      </c>
+      <c r="O131" s="1" t="inlineStr"/>
+      <c r="P131" s="1" t="inlineStr"/>
+      <c r="Q131" s="1" t="inlineStr"/>
+      <c r="R131" s="1" t="inlineStr"/>
+      <c r="S131" s="1" t="inlineStr"/>
+      <c r="T131" s="1" t="inlineStr"/>
+      <c r="U131" s="1" t="inlineStr"/>
+      <c r="V131" s="1" t="inlineStr"/>
+      <c r="W131" s="1" t="inlineStr"/>
+      <c r="X131" s="1" t="inlineStr"/>
+      <c r="Y131" s="1" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr"/>
+      <c r="B132" s="1" t="inlineStr"/>
+      <c r="C132" s="1" t="inlineStr"/>
+      <c r="D132" s="1" t="inlineStr"/>
+      <c r="E132" s="1" t="inlineStr"/>
+      <c r="F132" s="1" t="inlineStr"/>
+      <c r="G132" s="1" t="inlineStr"/>
+      <c r="H132" s="1" t="inlineStr"/>
+      <c r="I132" s="1" t="inlineStr"/>
+      <c r="J132" s="1" t="inlineStr"/>
+      <c r="K132" s="1" t="inlineStr"/>
+      <c r="L132" s="1" t="inlineStr"/>
+      <c r="M132" s="1" t="inlineStr"/>
+      <c r="N132" s="1" t="inlineStr">
+        <is>
+          <t>L1302: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
+      <c r="O132" s="1" t="inlineStr"/>
+      <c r="P132" s="1" t="inlineStr"/>
+      <c r="Q132" s="1" t="inlineStr"/>
+      <c r="R132" s="1" t="inlineStr"/>
+      <c r="S132" s="1" t="inlineStr"/>
+      <c r="T132" s="1" t="inlineStr"/>
+      <c r="U132" s="1" t="inlineStr"/>
+      <c r="V132" s="1" t="inlineStr"/>
+      <c r="W132" s="1" t="inlineStr"/>
+      <c r="X132" s="1" t="inlineStr"/>
+      <c r="Y132" s="1" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr"/>
+      <c r="B133" s="1" t="inlineStr"/>
+      <c r="C133" s="1" t="inlineStr"/>
+      <c r="D133" s="1" t="inlineStr"/>
+      <c r="E133" s="1" t="inlineStr"/>
+      <c r="F133" s="1" t="inlineStr"/>
+      <c r="G133" s="1" t="inlineStr"/>
+      <c r="H133" s="1" t="inlineStr"/>
+      <c r="I133" s="1" t="inlineStr"/>
+      <c r="J133" s="1" t="inlineStr"/>
+      <c r="K133" s="1" t="inlineStr"/>
+      <c r="L133" s="1" t="inlineStr"/>
+      <c r="M133" s="1" t="inlineStr"/>
+      <c r="N133" s="1" t="inlineStr">
+        <is>
+          <t>L1305: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="O133" s="1" t="inlineStr"/>
+      <c r="P133" s="1" t="inlineStr"/>
+      <c r="Q133" s="1" t="inlineStr"/>
+      <c r="R133" s="1" t="inlineStr"/>
+      <c r="S133" s="1" t="inlineStr"/>
+      <c r="T133" s="1" t="inlineStr"/>
+      <c r="U133" s="1" t="inlineStr"/>
+      <c r="V133" s="1" t="inlineStr"/>
+      <c r="W133" s="1" t="inlineStr"/>
+      <c r="X133" s="1" t="inlineStr"/>
+      <c r="Y133" s="1" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr"/>
+      <c r="B134" s="1" t="inlineStr"/>
+      <c r="C134" s="1" t="inlineStr"/>
+      <c r="D134" s="1" t="inlineStr"/>
+      <c r="E134" s="1" t="inlineStr"/>
+      <c r="F134" s="1" t="inlineStr"/>
+      <c r="G134" s="1" t="inlineStr"/>
+      <c r="H134" s="1" t="inlineStr"/>
+      <c r="I134" s="1" t="inlineStr"/>
+      <c r="J134" s="1" t="inlineStr"/>
+      <c r="K134" s="1" t="inlineStr"/>
+      <c r="L134" s="1" t="inlineStr"/>
+      <c r="M134" s="1" t="inlineStr"/>
+      <c r="N134" s="1" t="inlineStr">
+        <is>
+          <t>L1306: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
+      <c r="O134" s="1" t="inlineStr"/>
+      <c r="P134" s="1" t="inlineStr"/>
+      <c r="Q134" s="1" t="inlineStr"/>
+      <c r="R134" s="1" t="inlineStr"/>
+      <c r="S134" s="1" t="inlineStr"/>
+      <c r="T134" s="1" t="inlineStr"/>
+      <c r="U134" s="1" t="inlineStr"/>
+      <c r="V134" s="1" t="inlineStr"/>
+      <c r="W134" s="1" t="inlineStr"/>
+      <c r="X134" s="1" t="inlineStr"/>
+      <c r="Y134" s="1" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr"/>
+      <c r="B135" s="1" t="inlineStr"/>
+      <c r="C135" s="1" t="inlineStr"/>
+      <c r="D135" s="1" t="inlineStr"/>
+      <c r="E135" s="1" t="inlineStr"/>
+      <c r="F135" s="1" t="inlineStr"/>
+      <c r="G135" s="1" t="inlineStr"/>
+      <c r="H135" s="1" t="inlineStr"/>
+      <c r="I135" s="1" t="inlineStr"/>
+      <c r="J135" s="1" t="inlineStr"/>
+      <c r="K135" s="1" t="inlineStr"/>
+      <c r="L135" s="1" t="inlineStr"/>
+      <c r="M135" s="1" t="inlineStr"/>
+      <c r="N135" s="1" t="inlineStr">
+        <is>
+          <t>L1308: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="O135" s="1" t="inlineStr"/>
+      <c r="P135" s="1" t="inlineStr"/>
+      <c r="Q135" s="1" t="inlineStr"/>
+      <c r="R135" s="1" t="inlineStr"/>
+      <c r="S135" s="1" t="inlineStr"/>
+      <c r="T135" s="1" t="inlineStr"/>
+      <c r="U135" s="1" t="inlineStr"/>
+      <c r="V135" s="1" t="inlineStr"/>
+      <c r="W135" s="1" t="inlineStr"/>
+      <c r="X135" s="1" t="inlineStr"/>
+      <c r="Y135" s="1" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr"/>
+      <c r="B136" s="1" t="inlineStr"/>
+      <c r="C136" s="1" t="inlineStr"/>
+      <c r="D136" s="1" t="inlineStr"/>
+      <c r="E136" s="1" t="inlineStr"/>
+      <c r="F136" s="1" t="inlineStr"/>
+      <c r="G136" s="1" t="inlineStr"/>
+      <c r="H136" s="1" t="inlineStr"/>
+      <c r="I136" s="1" t="inlineStr"/>
+      <c r="J136" s="1" t="inlineStr"/>
+      <c r="K136" s="1" t="inlineStr"/>
+      <c r="L136" s="1" t="inlineStr"/>
+      <c r="M136" s="1" t="inlineStr"/>
+      <c r="N136" s="1" t="inlineStr">
+        <is>
+          <t>L1314: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
+      <c r="O136" s="1" t="inlineStr"/>
+      <c r="P136" s="1" t="inlineStr"/>
+      <c r="Q136" s="1" t="inlineStr"/>
+      <c r="R136" s="1" t="inlineStr"/>
+      <c r="S136" s="1" t="inlineStr"/>
+      <c r="T136" s="1" t="inlineStr"/>
+      <c r="U136" s="1" t="inlineStr"/>
+      <c r="V136" s="1" t="inlineStr"/>
+      <c r="W136" s="1" t="inlineStr"/>
+      <c r="X136" s="1" t="inlineStr"/>
+      <c r="Y136" s="1" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr"/>
+      <c r="B137" s="1" t="inlineStr"/>
+      <c r="C137" s="1" t="inlineStr"/>
+      <c r="D137" s="1" t="inlineStr"/>
+      <c r="E137" s="1" t="inlineStr"/>
+      <c r="F137" s="1" t="inlineStr"/>
+      <c r="G137" s="1" t="inlineStr"/>
+      <c r="H137" s="1" t="inlineStr"/>
+      <c r="I137" s="1" t="inlineStr"/>
+      <c r="J137" s="1" t="inlineStr"/>
+      <c r="K137" s="1" t="inlineStr"/>
+      <c r="L137" s="1" t="inlineStr"/>
+      <c r="M137" s="1" t="inlineStr"/>
+      <c r="N137" s="1" t="inlineStr">
+        <is>
+          <t>L1317: isolated marker/symbol line :: S</t>
+        </is>
+      </c>
+      <c r="O137" s="1" t="inlineStr"/>
+      <c r="P137" s="1" t="inlineStr"/>
+      <c r="Q137" s="1" t="inlineStr"/>
+      <c r="R137" s="1" t="inlineStr"/>
+      <c r="S137" s="1" t="inlineStr"/>
+      <c r="T137" s="1" t="inlineStr"/>
+      <c r="U137" s="1" t="inlineStr"/>
+      <c r="V137" s="1" t="inlineStr"/>
+      <c r="W137" s="1" t="inlineStr"/>
+      <c r="X137" s="1" t="inlineStr"/>
+      <c r="Y137" s="1" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr"/>
+      <c r="B138" s="1" t="inlineStr"/>
+      <c r="C138" s="1" t="inlineStr"/>
+      <c r="D138" s="1" t="inlineStr"/>
+      <c r="E138" s="1" t="inlineStr"/>
+      <c r="F138" s="1" t="inlineStr"/>
+      <c r="G138" s="1" t="inlineStr"/>
+      <c r="H138" s="1" t="inlineStr"/>
+      <c r="I138" s="1" t="inlineStr"/>
+      <c r="J138" s="1" t="inlineStr"/>
+      <c r="K138" s="1" t="inlineStr"/>
+      <c r="L138" s="1" t="inlineStr"/>
+      <c r="M138" s="1" t="inlineStr"/>
+      <c r="N138" s="1" t="inlineStr">
+        <is>
+          <t>L1318: isolated marker/symbol line :: '</t>
+        </is>
+      </c>
+      <c r="O138" s="1" t="inlineStr"/>
+      <c r="P138" s="1" t="inlineStr"/>
+      <c r="Q138" s="1" t="inlineStr"/>
+      <c r="R138" s="1" t="inlineStr"/>
+      <c r="S138" s="1" t="inlineStr"/>
+      <c r="T138" s="1" t="inlineStr"/>
+      <c r="U138" s="1" t="inlineStr"/>
+      <c r="V138" s="1" t="inlineStr"/>
+      <c r="W138" s="1" t="inlineStr"/>
+      <c r="X138" s="1" t="inlineStr"/>
+      <c r="Y138" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
